--- a/docs/0OMsoqOg9GiJ2xusVHMv/.gitbook/assets/IO - Template servizi - Legname.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHMv/.gitbook/assets/IO - Template servizi - Legname.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="122">
   <si>
     <r>
       <t xml:space="preserve">
@@ -1073,8 +1073,8 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t xml:space="preserve">
-Puoi pagare direttamente in app premendo “Vedi Avviso”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
-Se hai già provveduto a pagare l'avviso ignora questo messaggio.
+Puoi pagare direttamente in app premendo “Paga”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
+Se hai già provveduto a pagare l'avviso, ignora questo messaggio.
 Per maggiori informazioni o per richiedere assistenza, contattaci tramite i canali che trovi nella scheda servizio.
 In fase di pagamento, se previsto dall'ente, l'importo riportato nel messaggio potrebbe subire variazioni.</t>
     </r>
@@ -1210,6 +1210,9 @@
   </si>
   <si>
     <t>Vedi Avviso</t>
+  </si>
+  <si>
+    <t>Paga (inserito automaticamente dall'app se il messaggio prevede un avviso di pagamento pagoPA)</t>
   </si>
   <si>
     <r>
@@ -2091,18 +2094,18 @@
         <v>93</v>
       </c>
       <c r="H6" s="34" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I6" s="34" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J6" s="34" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B7" s="34" t="s">
         <v>59</v>
@@ -2134,10 +2137,10 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="32" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C8" s="34" t="s">
         <v>91</v>
@@ -2166,74 +2169,74 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="32" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F9" s="34" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G9" s="34" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H9" s="34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I9" s="34" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J9" s="34" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F10" s="34" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G10" s="34" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H10" s="34" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I10" s="34" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J10" s="34" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="32" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C11" s="34" t="s">
         <v>59</v>
@@ -2251,13 +2254,13 @@
         <v>59</v>
       </c>
       <c r="H11" s="34" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I11" s="34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J11" s="34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
